--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/201.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/201.xlsx
@@ -426,13 +426,13 @@
         <v>-12.52979158477232</v>
       </c>
       <c r="E2">
-        <v>-10.17273891669425</v>
+        <v>-20.82632271223735</v>
       </c>
       <c r="F2">
-        <v>7.808040897124317</v>
+        <v>4.31813111215491</v>
       </c>
       <c r="G2">
-        <v>-14.01995956620392</v>
+        <v>-18.76279608031308</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-12.35402668544163</v>
       </c>
       <c r="E3">
-        <v>-9.818336012379957</v>
+        <v>-21.09021500656034</v>
       </c>
       <c r="F3">
-        <v>8.451917125223124</v>
+        <v>4.661315432912892</v>
       </c>
       <c r="G3">
-        <v>-13.50794397200915</v>
+        <v>-20.66134097835648</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.10773210908172</v>
       </c>
       <c r="E4">
-        <v>-11.50341288995215</v>
+        <v>-21.75014952369814</v>
       </c>
       <c r="F4">
-        <v>7.817261232964006</v>
+        <v>3.472132832892227</v>
       </c>
       <c r="G4">
-        <v>-13.45807391400557</v>
+        <v>-18.48547333576111</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.79203841291045</v>
       </c>
       <c r="E5">
-        <v>-11.18808618785005</v>
+        <v>-20.9198085296517</v>
       </c>
       <c r="F5">
-        <v>8.000763653680059</v>
+        <v>3.796507478492535</v>
       </c>
       <c r="G5">
-        <v>-11.27998655062612</v>
+        <v>-18.03747376065924</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.39992607019381</v>
       </c>
       <c r="E6">
-        <v>-11.21707294997315</v>
+        <v>-22.22477435596806</v>
       </c>
       <c r="F6">
-        <v>8.233663445604584</v>
+        <v>3.993938592734878</v>
       </c>
       <c r="G6">
-        <v>-10.67535513442471</v>
+        <v>-17.028788606117</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.93750458106135</v>
       </c>
       <c r="E7">
-        <v>-12.43453054456528</v>
+        <v>-19.85406839973854</v>
       </c>
       <c r="F7">
-        <v>8.43485427769018</v>
+        <v>4.290286394749653</v>
       </c>
       <c r="G7">
-        <v>-10.56347855847058</v>
+        <v>-16.94952421427023</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.41594781201446</v>
       </c>
       <c r="E8">
-        <v>-15.03386103954605</v>
+        <v>-25.36357743100858</v>
       </c>
       <c r="F8">
-        <v>7.875243873940074</v>
+        <v>4.310481812583338</v>
       </c>
       <c r="G8">
-        <v>-8.85425051763594</v>
+        <v>-16.43679685278453</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-9.847672523388706</v>
       </c>
       <c r="E9">
-        <v>-12.99777761316532</v>
+        <v>-25.15027724829929</v>
       </c>
       <c r="F9">
-        <v>7.988415498657377</v>
+        <v>4.361727368595127</v>
       </c>
       <c r="G9">
-        <v>-5.733210536669255</v>
+        <v>-15.28071958974287</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.247941291046544</v>
       </c>
       <c r="E10">
-        <v>-14.34801459413636</v>
+        <v>-21.68791017693671</v>
       </c>
       <c r="F10">
-        <v>7.593179515576647</v>
+        <v>3.82387708412316</v>
       </c>
       <c r="G10">
-        <v>-6.445497583262225</v>
+        <v>-13.66158639048673</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-8.635024574663449</v>
       </c>
       <c r="E11">
-        <v>-14.79922268731261</v>
+        <v>-26.7545978488927</v>
       </c>
       <c r="F11">
-        <v>7.612269506681354</v>
+        <v>4.204704510785222</v>
       </c>
       <c r="G11">
-        <v>-5.520931735600107</v>
+        <v>-15.38630281862685</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.026299323943693</v>
       </c>
       <c r="E12">
-        <v>-15.81615039589709</v>
+        <v>-24.63209302454959</v>
       </c>
       <c r="F12">
-        <v>7.767046669503167</v>
+        <v>4.044804059326962</v>
       </c>
       <c r="G12">
-        <v>-6.939037022802313</v>
+        <v>-11.77509187820628</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.439470735822586</v>
       </c>
       <c r="E13">
-        <v>-16.78922436219129</v>
+        <v>-25.81242618922685</v>
       </c>
       <c r="F13">
-        <v>7.357484482711372</v>
+        <v>4.255410023079846</v>
       </c>
       <c r="G13">
-        <v>-4.040862967539363</v>
+        <v>-13.85229698736753</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.899889783011592</v>
       </c>
       <c r="E14">
-        <v>-17.07181925416595</v>
+        <v>-26.71747341897782</v>
       </c>
       <c r="F14">
-        <v>7.634585506735812</v>
+        <v>4.123580758972752</v>
       </c>
       <c r="G14">
-        <v>-4.325814864286591</v>
+        <v>-11.9750686920515</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.422901077636612</v>
       </c>
       <c r="E15">
-        <v>-19.27906088414059</v>
+        <v>-28.91339386393328</v>
       </c>
       <c r="F15">
-        <v>7.337680240238801</v>
+        <v>3.848899637587103</v>
       </c>
       <c r="G15">
-        <v>-2.138113676661091</v>
+        <v>-11.10271014754368</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.018966004571133</v>
       </c>
       <c r="E16">
-        <v>-18.70917054417131</v>
+        <v>-28.46145668644179</v>
       </c>
       <c r="F16">
-        <v>7.864373316536498</v>
+        <v>3.905018256700699</v>
       </c>
       <c r="G16">
-        <v>-1.780849533699562</v>
+        <v>-10.25353204290185</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.693379109148515</v>
       </c>
       <c r="E17">
-        <v>-20.90267731248068</v>
+        <v>-30.00687316138043</v>
       </c>
       <c r="F17">
-        <v>7.676864119854383</v>
+        <v>4.748363828555021</v>
       </c>
       <c r="G17">
-        <v>-1.471085098135496</v>
+        <v>-10.94923325634307</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.444340156995622</v>
       </c>
       <c r="E18">
-        <v>-20.36105370726728</v>
+        <v>-27.31053596044435</v>
       </c>
       <c r="F18">
-        <v>8.345997289892619</v>
+        <v>4.268961794598262</v>
       </c>
       <c r="G18">
-        <v>-1.382465104594746</v>
+        <v>-8.82028100985748</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.266602142083448</v>
       </c>
       <c r="E19">
-        <v>-22.10692987686645</v>
+        <v>-30.57041005231695</v>
       </c>
       <c r="F19">
-        <v>8.431686865859302</v>
+        <v>4.291293631711874</v>
       </c>
       <c r="G19">
-        <v>-1.876742795790091</v>
+        <v>-10.52961167760383</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.158292937862517</v>
       </c>
       <c r="E20">
-        <v>-23.96078298070452</v>
+        <v>-34.20866531837445</v>
       </c>
       <c r="F20">
-        <v>8.070288343367851</v>
+        <v>5.220911583309759</v>
       </c>
       <c r="G20">
-        <v>-1.488793206225058</v>
+        <v>-9.388178612755137</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.11375336039121</v>
       </c>
       <c r="E21">
-        <v>-22.98528175234221</v>
+        <v>-33.97300126677828</v>
       </c>
       <c r="F21">
-        <v>8.618863484299174</v>
+        <v>4.4722494533159</v>
       </c>
       <c r="G21">
-        <v>-1.626316578471922</v>
+        <v>-7.443147034249294</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.12498876591109</v>
       </c>
       <c r="E22">
-        <v>-25.43079357070443</v>
+        <v>-33.98722293939937</v>
       </c>
       <c r="F22">
-        <v>8.810121312883135</v>
+        <v>4.479992191536484</v>
       </c>
       <c r="G22">
-        <v>-0.5358758465646217</v>
+        <v>-7.126953519247963</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.183325988094308</v>
       </c>
       <c r="E23">
-        <v>-24.23589683361851</v>
+        <v>-33.09008242526578</v>
       </c>
       <c r="F23">
-        <v>8.3345375938885</v>
+        <v>4.680739585965757</v>
       </c>
       <c r="G23">
-        <v>0.5221347812399785</v>
+        <v>-8.351924890234628</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.278588348714838</v>
       </c>
       <c r="E24">
-        <v>-23.95643111718315</v>
+        <v>-33.93844901009975</v>
       </c>
       <c r="F24">
-        <v>8.938140180557683</v>
+        <v>4.946002408272287</v>
       </c>
       <c r="G24">
-        <v>-0.364912653825579</v>
+        <v>-7.938818465116672</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.399763686971659</v>
       </c>
       <c r="E25">
-        <v>-25.72890754310338</v>
+        <v>-33.02397576170181</v>
       </c>
       <c r="F25">
-        <v>8.237619542981351</v>
+        <v>4.682719218360056</v>
       </c>
       <c r="G25">
-        <v>1.184608049103536</v>
+        <v>-6.614411548312459</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.539961763441961</v>
       </c>
       <c r="E26">
-        <v>-24.19688403004243</v>
+        <v>-35.55122200742848</v>
       </c>
       <c r="F26">
-        <v>8.562548485652064</v>
+        <v>4.815283322011915</v>
       </c>
       <c r="G26">
-        <v>-0.06678147528651229</v>
+        <v>-7.207247490757447</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.692222937705623</v>
       </c>
       <c r="E27">
-        <v>-26.30659591531387</v>
+        <v>-32.70134236678834</v>
       </c>
       <c r="F27">
-        <v>8.954050090184188</v>
+        <v>5.395257016422741</v>
       </c>
       <c r="G27">
-        <v>0.2716357319199455</v>
+        <v>-5.812282916874747</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.84794682458903</v>
       </c>
       <c r="E28">
-        <v>-24.89802766065003</v>
+        <v>-34.81781526375323</v>
       </c>
       <c r="F28">
-        <v>8.560708219378322</v>
+        <v>4.523396819560933</v>
       </c>
       <c r="G28">
-        <v>-0.0855787528584941</v>
+        <v>-8.395455253530503</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.999267888796469</v>
       </c>
       <c r="E29">
-        <v>-25.84175258690052</v>
+        <v>-34.13031818956775</v>
       </c>
       <c r="F29">
-        <v>8.986891399752656</v>
+        <v>4.407724523203151</v>
       </c>
       <c r="G29">
-        <v>-0.162118565726444</v>
+        <v>-7.295069642823233</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.138896980239611</v>
       </c>
       <c r="E30">
-        <v>-25.51653569756566</v>
+        <v>-33.47804585045092</v>
       </c>
       <c r="F30">
-        <v>8.406072006382985</v>
+        <v>4.788935206696749</v>
       </c>
       <c r="G30">
-        <v>0.3623546113325939</v>
+        <v>-4.895963638150953</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.258519461758904</v>
       </c>
       <c r="E31">
-        <v>-27.04950113322021</v>
+        <v>-35.52847774672495</v>
       </c>
       <c r="F31">
-        <v>8.941651256572211</v>
+        <v>5.221644839148608</v>
       </c>
       <c r="G31">
-        <v>-1.339583608224566</v>
+        <v>-7.348753449288054</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.355171725081768</v>
       </c>
       <c r="E32">
-        <v>-26.0601246604984</v>
+        <v>-33.42283922382341</v>
       </c>
       <c r="F32">
-        <v>8.93888452233794</v>
+        <v>5.119929743023594</v>
       </c>
       <c r="G32">
-        <v>-0.4479543781326575</v>
+        <v>-6.331402941796783</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.429927399457323</v>
       </c>
       <c r="E33">
-        <v>-25.387437960555</v>
+        <v>-34.36953935749694</v>
       </c>
       <c r="F33">
-        <v>9.052599358184237</v>
+        <v>4.653680386694559</v>
       </c>
       <c r="G33">
-        <v>-1.082678653286044</v>
+        <v>-7.583408227657135</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.482816815799613</v>
       </c>
       <c r="E34">
-        <v>-24.42790413154373</v>
+        <v>-33.99859167339562</v>
       </c>
       <c r="F34">
-        <v>8.850569161963458</v>
+        <v>4.556483603546293</v>
       </c>
       <c r="G34">
-        <v>-0.09081934644716039</v>
+        <v>-5.806972801829756</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.515412257844766</v>
       </c>
       <c r="E35">
-        <v>-24.9050332099399</v>
+        <v>-34.28027860633175</v>
       </c>
       <c r="F35">
-        <v>9.035259362116092</v>
+        <v>4.867916204405629</v>
       </c>
       <c r="G35">
-        <v>-1.263739009919863</v>
+        <v>-8.345747412258348</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.529698620152431</v>
       </c>
       <c r="E36">
-        <v>-24.63531276956904</v>
+        <v>-32.44894107525982</v>
       </c>
       <c r="F36">
-        <v>9.601777891069345</v>
+        <v>5.15914388519579</v>
       </c>
       <c r="G36">
-        <v>-1.95124331260585</v>
+        <v>-6.833480278282651</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.525649373982487</v>
       </c>
       <c r="E37">
-        <v>-24.99326146903134</v>
+        <v>-31.3045277664114</v>
       </c>
       <c r="F37">
-        <v>9.64039814352325</v>
+        <v>5.469976261513175</v>
       </c>
       <c r="G37">
-        <v>-1.781379220985845</v>
+        <v>-8.339500412825743</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.504374230262417</v>
       </c>
       <c r="E38">
-        <v>-23.79304830346041</v>
+        <v>-33.90586211114056</v>
       </c>
       <c r="F38">
-        <v>9.023145595568895</v>
+        <v>5.255825963921537</v>
       </c>
       <c r="G38">
-        <v>-1.952733058098522</v>
+        <v>-9.451406722009677</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.470385087921263</v>
       </c>
       <c r="E39">
-        <v>-21.8406918330075</v>
+        <v>-32.75755205040854</v>
       </c>
       <c r="F39">
-        <v>9.077032773047637</v>
+        <v>5.474044802009939</v>
       </c>
       <c r="G39">
-        <v>-4.020493180836227</v>
+        <v>-7.388983198681277</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.425499186676762</v>
       </c>
       <c r="E40">
-        <v>-20.71816916751216</v>
+        <v>-32.7169089961897</v>
       </c>
       <c r="F40">
-        <v>9.774379663969427</v>
+        <v>6.266081469615854</v>
       </c>
       <c r="G40">
-        <v>-2.851244912366576</v>
+        <v>-8.106133436671438</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.370589224857603</v>
       </c>
       <c r="E41">
-        <v>-21.47310654085688</v>
+        <v>-31.70695287334003</v>
       </c>
       <c r="F41">
-        <v>9.352182671384256</v>
+        <v>4.783571194761156</v>
       </c>
       <c r="G41">
-        <v>-2.400878297204124</v>
+        <v>-10.06549967736233</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.306126939852138</v>
       </c>
       <c r="E42">
-        <v>-19.84718511924688</v>
+        <v>-27.95270980252407</v>
       </c>
       <c r="F42">
-        <v>9.001187513051327</v>
+        <v>5.634344347358889</v>
       </c>
       <c r="G42">
-        <v>-2.629024543042997</v>
+        <v>-12.18969135936245</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.231116116920788</v>
       </c>
       <c r="E43">
-        <v>-20.2036122514426</v>
+        <v>-29.35018782434313</v>
       </c>
       <c r="F43">
-        <v>9.245862158457145</v>
+        <v>5.936303219432066</v>
       </c>
       <c r="G43">
-        <v>-4.151011438721993</v>
+        <v>-10.35850944195214</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.144699348881297</v>
       </c>
       <c r="E44">
-        <v>-17.87317348608929</v>
+        <v>-28.51403679814485</v>
       </c>
       <c r="F44">
-        <v>9.558710592404884</v>
+        <v>6.664000250517338</v>
       </c>
       <c r="G44">
-        <v>-3.914002862474491</v>
+        <v>-10.62102577157973</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.049710715330298</v>
       </c>
       <c r="E45">
-        <v>-18.18043497598373</v>
+        <v>-27.58388823696936</v>
       </c>
       <c r="F45">
-        <v>9.611174018265647</v>
+        <v>6.121818530366643</v>
       </c>
       <c r="G45">
-        <v>-4.478182722731547</v>
+        <v>-10.3506833122973</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.949771793395087</v>
       </c>
       <c r="E46">
-        <v>-19.36662798602691</v>
+        <v>-29.69692402216243</v>
       </c>
       <c r="F46">
-        <v>10.31535460021256</v>
+        <v>6.212305151551192</v>
       </c>
       <c r="G46">
-        <v>-3.07026067360814</v>
+        <v>-9.565835728574585</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.846966478314061</v>
       </c>
       <c r="E47">
-        <v>-17.12677681472304</v>
+        <v>-27.84711937408722</v>
       </c>
       <c r="F47">
-        <v>9.473812869395921</v>
+        <v>5.863921524272822</v>
       </c>
       <c r="G47">
-        <v>-2.960261176974776</v>
+        <v>-10.50984772073438</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.743299210492927</v>
       </c>
       <c r="E48">
-        <v>-17.90321991113018</v>
+        <v>-26.26879221429784</v>
       </c>
       <c r="F48">
-        <v>9.885997673183684</v>
+        <v>5.834103509296928</v>
       </c>
       <c r="G48">
-        <v>-2.920918653786077</v>
+        <v>-12.3653257318574</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.640302750383928</v>
       </c>
       <c r="E49">
-        <v>-16.35497993264777</v>
+        <v>-24.7146969189235</v>
       </c>
       <c r="F49">
-        <v>9.860365392942297</v>
+        <v>6.125495895502294</v>
       </c>
       <c r="G49">
-        <v>-2.915959456568249</v>
+        <v>-10.7900191897229</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.537974266808901</v>
       </c>
       <c r="E50">
-        <v>-16.82219165296713</v>
+        <v>-24.37062799229472</v>
       </c>
       <c r="F50">
-        <v>10.11328956246164</v>
+        <v>5.727627793190103</v>
       </c>
       <c r="G50">
-        <v>-3.582332547077068</v>
+        <v>-12.05013531215447</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.439005356361401</v>
       </c>
       <c r="E51">
-        <v>-14.05453325064726</v>
+        <v>-25.69636140041025</v>
       </c>
       <c r="F51">
-        <v>10.46804760604965</v>
+        <v>6.114348189563516</v>
       </c>
       <c r="G51">
-        <v>-4.521534316568303</v>
+        <v>-10.46984639898337</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.349578373114531</v>
       </c>
       <c r="E52">
-        <v>-14.62074646972231</v>
+        <v>-20.42396779665584</v>
       </c>
       <c r="F52">
-        <v>10.04196895026574</v>
+        <v>6.727451428019419</v>
       </c>
       <c r="G52">
-        <v>-4.779780042450231</v>
+        <v>-12.132203736073</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.272890457620179</v>
       </c>
       <c r="E53">
-        <v>-13.30303298907436</v>
+        <v>-23.20274360266455</v>
       </c>
       <c r="F53">
-        <v>9.893618466048778</v>
+        <v>6.861212813343351</v>
       </c>
       <c r="G53">
-        <v>-4.625584762867597</v>
+        <v>-11.79001581749731</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.21176596190941</v>
       </c>
       <c r="E54">
-        <v>-12.65265355209274</v>
+        <v>-22.03618605591863</v>
       </c>
       <c r="F54">
-        <v>10.12620785161388</v>
+        <v>6.441099977742898</v>
       </c>
       <c r="G54">
-        <v>-2.822506066540162</v>
+        <v>-11.27980116007592</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.168219154718102</v>
       </c>
       <c r="E55">
-        <v>-13.4188305979245</v>
+        <v>-19.1810601781406</v>
       </c>
       <c r="F55">
-        <v>10.23999870534412</v>
+        <v>6.746782142423274</v>
       </c>
       <c r="G55">
-        <v>-3.765121008482387</v>
+        <v>-11.08264162048462</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.140840230652588</v>
       </c>
       <c r="E56">
-        <v>-11.90437756401331</v>
+        <v>-19.2336040620516</v>
       </c>
       <c r="F56">
-        <v>10.14370146715582</v>
+        <v>6.263555458680727</v>
       </c>
       <c r="G56">
-        <v>-3.340778591804145</v>
+        <v>-12.92434776216427</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.129235380447684</v>
       </c>
       <c r="E57">
-        <v>-12.1369282897292</v>
+        <v>-18.53595641337792</v>
       </c>
       <c r="F57">
-        <v>10.47953264134842</v>
+        <v>6.20739566321333</v>
       </c>
       <c r="G57">
-        <v>-3.763247239707159</v>
+        <v>-12.88390613785654</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.135251507533296</v>
       </c>
       <c r="E58">
-        <v>-11.38409665679805</v>
+        <v>-22.93152876587116</v>
       </c>
       <c r="F58">
-        <v>9.976612574547383</v>
+        <v>6.419293930993212</v>
       </c>
       <c r="G58">
-        <v>-3.845510985812509</v>
+        <v>-10.94024181465841</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.157908629537375</v>
       </c>
       <c r="E59">
-        <v>-10.57067404164427</v>
+        <v>-18.81086195648755</v>
       </c>
       <c r="F59">
-        <v>10.39204872657954</v>
+        <v>6.738044836887794</v>
       </c>
       <c r="G59">
-        <v>-3.825425906025751</v>
+        <v>-12.53873541774997</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.194659910255082</v>
       </c>
       <c r="E60">
-        <v>-9.676513263407736</v>
+        <v>-21.95264476742512</v>
       </c>
       <c r="F60">
-        <v>10.19501037140423</v>
+        <v>6.439647719418439</v>
       </c>
       <c r="G60">
-        <v>-2.550024994839369</v>
+        <v>-11.15838028133207</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.242284217357399</v>
       </c>
       <c r="E61">
-        <v>-10.3618706336246</v>
+        <v>-17.89635021606055</v>
       </c>
       <c r="F61">
-        <v>10.03753615740842</v>
+        <v>6.692375509404267</v>
       </c>
       <c r="G61">
-        <v>-4.167968052974141</v>
+        <v>-11.31938204254345</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.29527362031261</v>
       </c>
       <c r="E62">
-        <v>-10.68942421554741</v>
+        <v>-17.62993556171529</v>
       </c>
       <c r="F62">
-        <v>10.5838703544694</v>
+        <v>6.36794860150875</v>
       </c>
       <c r="G62">
-        <v>-4.305852274684786</v>
+        <v>-11.72508939838113</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.348512456991937</v>
       </c>
       <c r="E63">
-        <v>-7.409708614810209</v>
+        <v>-16.63559135300707</v>
       </c>
       <c r="F63">
-        <v>10.82143574402081</v>
+        <v>6.555909154376764</v>
       </c>
       <c r="G63">
-        <v>-4.46808555883677</v>
+        <v>-11.74179772171783</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.400408005816086</v>
       </c>
       <c r="E64">
-        <v>-7.932004692958877</v>
+        <v>-18.33249207621329</v>
       </c>
       <c r="F64">
-        <v>10.66443189068189</v>
+        <v>6.376207627857767</v>
       </c>
       <c r="G64">
-        <v>-4.17101375487027</v>
+        <v>-13.48954892572019</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.449550828613641</v>
       </c>
       <c r="E65">
-        <v>-8.637545471827927</v>
+        <v>-18.17078026939938</v>
       </c>
       <c r="F65">
-        <v>10.32401430415818</v>
+        <v>5.538477877179592</v>
       </c>
       <c r="G65">
-        <v>-4.37805527289629</v>
+        <v>-10.76707048804468</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.493314318065105</v>
       </c>
       <c r="E66">
-        <v>-7.161267473801398</v>
+        <v>-17.9895416826644</v>
       </c>
       <c r="F66">
-        <v>10.36664608369589</v>
+        <v>5.458351860093849</v>
       </c>
       <c r="G66">
-        <v>-4.171136245055223</v>
+        <v>-12.60114582225631</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.528801828212276</v>
       </c>
       <c r="E67">
-        <v>-6.289672081545084</v>
+        <v>-16.46556073944107</v>
       </c>
       <c r="F67">
-        <v>10.33954095695315</v>
+        <v>5.833260977749914</v>
       </c>
       <c r="G67">
-        <v>-4.389595834646189</v>
+        <v>-14.52922906287385</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.5528523917542</v>
       </c>
       <c r="E68">
-        <v>-7.012099539988736</v>
+        <v>-15.69765381653838</v>
       </c>
       <c r="F68">
-        <v>10.57125138573518</v>
+        <v>5.954642533932855</v>
       </c>
       <c r="G68">
-        <v>-4.254810283560302</v>
+        <v>-11.90894385545009</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.561196353401214</v>
       </c>
       <c r="E69">
-        <v>-7.502673657713673</v>
+        <v>-16.28329871758035</v>
       </c>
       <c r="F69">
-        <v>10.40267222586031</v>
+        <v>6.158408471836956</v>
       </c>
       <c r="G69">
-        <v>-3.685230923528695</v>
+        <v>-13.02762023026184</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.552896951685033</v>
       </c>
       <c r="E70">
-        <v>-8.165846033766959</v>
+        <v>-15.02838158599677</v>
       </c>
       <c r="F70">
-        <v>10.4528915404389</v>
+        <v>5.710457253654909</v>
       </c>
       <c r="G70">
-        <v>-5.271743662313626</v>
+        <v>-13.04428551650653</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.529395740450531</v>
       </c>
       <c r="E71">
-        <v>-7.782257114473234</v>
+        <v>-19.30088360038356</v>
       </c>
       <c r="F71">
-        <v>10.33383644824574</v>
+        <v>5.539274481255059</v>
       </c>
       <c r="G71">
-        <v>-5.26595351816544</v>
+        <v>-13.45412774372276</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.490803288953771</v>
       </c>
       <c r="E72">
-        <v>-7.23783038384908</v>
+        <v>-15.78076942847516</v>
       </c>
       <c r="F72">
-        <v>10.52389382774579</v>
+        <v>5.45494847608157</v>
       </c>
       <c r="G72">
-        <v>-4.80240762121115</v>
+        <v>-14.08708584283095</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.437849390730749</v>
       </c>
       <c r="E73">
-        <v>-6.64423801092365</v>
+        <v>-15.49364606249283</v>
       </c>
       <c r="F73">
-        <v>10.44825128210666</v>
+        <v>5.569132088878838</v>
       </c>
       <c r="G73">
-        <v>-5.733293300307736</v>
+        <v>-14.35856547450611</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.372615952683758</v>
       </c>
       <c r="E74">
-        <v>-6.989484340794431</v>
+        <v>-15.92655006373009</v>
       </c>
       <c r="F74">
-        <v>9.137067896890116</v>
+        <v>4.97174079681001</v>
       </c>
       <c r="G74">
-        <v>-4.869217740739181</v>
+        <v>-11.35378192124201</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.295540010606801</v>
       </c>
       <c r="E75">
-        <v>-5.912527180764274</v>
+        <v>-17.84299573530217</v>
       </c>
       <c r="F75">
-        <v>9.659651256337249</v>
+        <v>5.3691781311132</v>
       </c>
       <c r="G75">
-        <v>-3.707083834633424</v>
+        <v>-10.79428979346856</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.210144502139257</v>
       </c>
       <c r="E76">
-        <v>-7.16651144670228</v>
+        <v>-14.80613313864832</v>
       </c>
       <c r="F76">
-        <v>9.837523602523914</v>
+        <v>5.727686390308974</v>
       </c>
       <c r="G76">
-        <v>-4.313966421801539</v>
+        <v>-11.83294697205058</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.123627054778824</v>
       </c>
       <c r="E77">
-        <v>-8.436666893321677</v>
+        <v>-18.42819231741738</v>
       </c>
       <c r="F77">
-        <v>9.654749686528962</v>
+        <v>5.435628847619124</v>
       </c>
       <c r="G77">
-        <v>-5.813597203453837</v>
+        <v>-10.64256418085822</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.041238270359098</v>
       </c>
       <c r="E78">
-        <v>-9.273347750978852</v>
+        <v>-16.64028738055302</v>
       </c>
       <c r="F78">
-        <v>9.250632280674449</v>
+        <v>5.338028219462422</v>
       </c>
       <c r="G78">
-        <v>-3.876226227325867</v>
+        <v>-10.31887890130152</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.967657402945815</v>
       </c>
       <c r="E79">
-        <v>-8.239646574669964</v>
+        <v>-16.665071718797</v>
       </c>
       <c r="F79">
-        <v>9.022068675546397</v>
+        <v>5.056030376747443</v>
       </c>
       <c r="G79">
-        <v>-3.688366010154384</v>
+        <v>-10.97089415580652</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.906974510469992</v>
       </c>
       <c r="E80">
-        <v>-8.802323055545028</v>
+        <v>-20.14642668167374</v>
       </c>
       <c r="F80">
-        <v>9.753957776189836</v>
+        <v>4.966376784874416</v>
       </c>
       <c r="G80">
-        <v>-4.164028503782408</v>
+        <v>-10.76888135645466</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.861052194618159</v>
       </c>
       <c r="E81">
-        <v>-8.969998862627039</v>
+        <v>-17.13193927509178</v>
       </c>
       <c r="F81">
-        <v>9.366341002268285</v>
+        <v>5.331192944731385</v>
       </c>
       <c r="G81">
-        <v>-3.649304883336524</v>
+        <v>-11.35095471535147</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.831323066399488</v>
       </c>
       <c r="E82">
-        <v>-11.84820184394816</v>
+        <v>-16.37438897224464</v>
       </c>
       <c r="F82">
-        <v>8.708917753768807</v>
+        <v>4.420565210765534</v>
       </c>
       <c r="G82">
-        <v>-2.951484920750168</v>
+        <v>-10.05038372643001</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.822494530370428</v>
       </c>
       <c r="E83">
-        <v>-10.36644439237235</v>
+        <v>-16.22387155317769</v>
       </c>
       <c r="F83">
-        <v>9.193973617843687</v>
+        <v>5.154319916977362</v>
       </c>
       <c r="G83">
-        <v>-3.590595668743088</v>
+        <v>-12.2185096582818</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.838035303457738</v>
       </c>
       <c r="E84">
-        <v>-11.89609045657927</v>
+        <v>-17.46024458369987</v>
       </c>
       <c r="F84">
-        <v>8.824529869301802</v>
+        <v>4.31223814244356</v>
       </c>
       <c r="G84">
-        <v>-3.557394207529738</v>
+        <v>-9.856564527287842</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.880014303322711</v>
       </c>
       <c r="E85">
-        <v>-11.93305638990388</v>
+        <v>-20.57563544812074</v>
       </c>
       <c r="F85">
-        <v>8.724225855147445</v>
+        <v>4.482226800583168</v>
       </c>
       <c r="G85">
-        <v>-3.388235262109598</v>
+        <v>-9.646818293556239</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.949878942463882</v>
       </c>
       <c r="E86">
-        <v>-11.96413077854452</v>
+        <v>-18.82399905958381</v>
       </c>
       <c r="F86">
-        <v>8.804016126579116</v>
+        <v>4.676378059874637</v>
       </c>
       <c r="G86">
-        <v>-2.183650230553766</v>
+        <v>-10.26049743071648</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.047551334181902</v>
       </c>
       <c r="E87">
-        <v>-12.88779003646702</v>
+        <v>-20.38478291106747</v>
       </c>
       <c r="F87">
-        <v>8.196797939304984</v>
+        <v>3.827144269426711</v>
       </c>
       <c r="G87">
-        <v>-2.632338399127808</v>
+        <v>-7.997097308790002</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.170937833837158</v>
       </c>
       <c r="E88">
-        <v>-14.19856136646121</v>
+        <v>-22.00900162645058</v>
       </c>
       <c r="F88">
-        <v>7.841382657762064</v>
+        <v>3.726021479314071</v>
       </c>
       <c r="G88">
-        <v>-0.7627740167351903</v>
+        <v>-8.194445549477036</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.321392860857251</v>
       </c>
       <c r="E89">
-        <v>-18.09193047997782</v>
+        <v>-25.45191437347621</v>
       </c>
       <c r="F89">
-        <v>8.314331090113408</v>
+        <v>4.157711205156387</v>
       </c>
       <c r="G89">
-        <v>-2.254979244742903</v>
+        <v>-5.963422562924634</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.500075031606745</v>
       </c>
       <c r="E90">
-        <v>-18.6915728941775</v>
+        <v>-25.50366124596186</v>
       </c>
       <c r="F90">
-        <v>7.761731752450952</v>
+        <v>3.982763963795537</v>
       </c>
       <c r="G90">
-        <v>-1.713162119603624</v>
+        <v>-7.10929837988703</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.705048494845172</v>
       </c>
       <c r="E91">
-        <v>-19.81232492633584</v>
+        <v>-26.76479597235798</v>
       </c>
       <c r="F91">
-        <v>7.321952456792572</v>
+        <v>3.363262553441258</v>
       </c>
       <c r="G91">
-        <v>-0.1406728517230452</v>
+        <v>-7.8931726632212</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.932978414084146</v>
       </c>
       <c r="E92">
-        <v>-20.40301907589636</v>
+        <v>-28.45436056767177</v>
       </c>
       <c r="F92">
-        <v>6.686677335520516</v>
+        <v>3.152960661224138</v>
       </c>
       <c r="G92">
-        <v>-1.796385923915362</v>
+        <v>-8.307907876744478</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.17908155606955</v>
       </c>
       <c r="E93">
-        <v>-22.05438599295545</v>
+        <v>-29.54184869400677</v>
       </c>
       <c r="F93">
-        <v>6.383402403831608</v>
+        <v>3.024731160662837</v>
       </c>
       <c r="G93">
-        <v>-1.829229846210471</v>
+        <v>-6.25188032739795</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.433478126874307</v>
       </c>
       <c r="E94">
-        <v>-24.34532287953986</v>
+        <v>-31.42488328435026</v>
       </c>
       <c r="F94">
-        <v>6.783289731185984</v>
+        <v>2.332003939896384</v>
       </c>
       <c r="G94">
-        <v>-0.4846716387087142</v>
+        <v>-6.291934617877592</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.691215573081624</v>
       </c>
       <c r="E95">
-        <v>-25.41921879114083</v>
+        <v>-30.16132129588603</v>
       </c>
       <c r="F95">
-        <v>5.917677254160583</v>
+        <v>2.536883223059039</v>
       </c>
       <c r="G95">
-        <v>-1.3547856333409</v>
+        <v>-8.291924562880876</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.950427282479683</v>
       </c>
       <c r="E96">
-        <v>-29.14159272612781</v>
+        <v>-33.00296137806922</v>
       </c>
       <c r="F96">
-        <v>5.371618621928892</v>
+        <v>1.072777194647663</v>
       </c>
       <c r="G96">
-        <v>-0.03913510948805862</v>
+        <v>-5.592528903977925</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-7.204761729548567</v>
       </c>
       <c r="E97">
-        <v>-29.74111740000329</v>
+        <v>-35.98161949830249</v>
       </c>
       <c r="F97">
-        <v>4.6797592720041</v>
+        <v>0.5613779663753647</v>
       </c>
       <c r="G97">
-        <v>0.4559338020911725</v>
+        <v>-4.33213138517552</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.453535341328745</v>
       </c>
       <c r="E98">
-        <v>-32.46299972281663</v>
+        <v>-36.60938600032681</v>
       </c>
       <c r="F98">
-        <v>4.616434790975254</v>
+        <v>1.853081768832002</v>
       </c>
       <c r="G98">
-        <v>0.6752309597035745</v>
+        <v>-7.295887347571433</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.688702389051675</v>
       </c>
       <c r="E99">
-        <v>-35.84375463561297</v>
+        <v>-39.55320657001906</v>
       </c>
       <c r="F99">
-        <v>4.158357357169886</v>
+        <v>1.90594270487754</v>
       </c>
       <c r="G99">
-        <v>1.292442448954216</v>
+        <v>-5.292451124661767</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.913030655969816</v>
       </c>
       <c r="E100">
-        <v>-37.30965110697692</v>
+        <v>-40.13938809523094</v>
       </c>
       <c r="F100">
-        <v>3.474152057934413</v>
+        <v>0.2382465299186771</v>
       </c>
       <c r="G100">
-        <v>-0.147787214086939</v>
+        <v>-6.052459685203332</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.11213039851545</v>
       </c>
       <c r="E101">
-        <v>-38.85602535416817</v>
+        <v>-43.96764680946527</v>
       </c>
       <c r="F101">
-        <v>3.400104304152126</v>
+        <v>0.675559995466718</v>
       </c>
       <c r="G101">
-        <v>0.3196816793313882</v>
+        <v>-7.247904300525236</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.309140308385812</v>
       </c>
       <c r="E102">
-        <v>-39.66081669786334</v>
+        <v>-47.34579105699619</v>
       </c>
       <c r="F102">
-        <v>3.448106430449096</v>
+        <v>0.007580555187879263</v>
       </c>
       <c r="G102">
-        <v>0.51054456130699</v>
+        <v>-7.232112998302912</v>
       </c>
     </row>
   </sheetData>
